--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,10 +568,10 @@
         <v>353586.41</v>
       </c>
       <c r="E3" t="n">
-        <v>273584.33</v>
+        <v>345872.73</v>
       </c>
       <c r="F3" t="n">
-        <v>273584.33</v>
+        <v>345872.73</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -586,7 +586,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>273584.33</v>
+        <v>345872.73</v>
       </c>
     </row>
     <row r="4">
@@ -605,10 +605,10 @@
         <v>6030471.4</v>
       </c>
       <c r="E4" t="n">
-        <v>6000116.51</v>
+        <v>6028400.95</v>
       </c>
       <c r="F4" t="n">
-        <v>5500116.51</v>
+        <v>5528400.95</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -623,7 +623,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>5500116.51</v>
+        <v>5528400.95</v>
       </c>
     </row>
     <row r="5">
@@ -734,13 +734,13 @@
         <v>377200278.81</v>
       </c>
       <c r="E7" t="n">
-        <v>177735186.86</v>
+        <v>183039448.59</v>
       </c>
       <c r="F7" t="n">
-        <v>167991587.27</v>
+        <v>170878454.75</v>
       </c>
       <c r="G7" t="n">
-        <v>17505440.57</v>
+        <v>19134958.28</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -770,7 +770,7 @@
         <v>22345704.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>190337291.99</v>
+        <v>193224159.47</v>
       </c>
     </row>
     <row r="8">
@@ -789,10 +789,10 @@
         <v>63156.57</v>
       </c>
       <c r="E8" t="n">
-        <v>50432.87</v>
+        <v>63156.57</v>
       </c>
       <c r="F8" t="n">
-        <v>39400.43</v>
+        <v>52124.13</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -807,7 +807,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>39400.43</v>
+        <v>52124.13</v>
       </c>
     </row>
     <row r="9">
@@ -815,15 +815,15 @@
         <v>9456627</v>
       </c>
       <c r="B9" t="n">
-        <v>1401</v>
+        <v>1251</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2400949</v>
+        <v>14888.88</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -831,38 +831,20 @@
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
-        <v>172000</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>2400949</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>169987.02</v>
-      </c>
-      <c r="P9" t="n">
-        <v>169987.02</v>
-      </c>
+        <v>14888.88</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>169987.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -870,91 +852,91 @@
         <v>9456627</v>
       </c>
       <c r="B10" t="n">
-        <v>1511</v>
+        <v>1401</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>287221.89</v>
+        <v>2400949</v>
       </c>
       <c r="E10" t="n">
-        <v>126290.67</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>124982.21</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>172000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="M10" t="n">
-        <v>287221.89</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+        <v>2400949</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>169987.02</v>
+      </c>
+      <c r="P10" t="n">
+        <v>169987.02</v>
+      </c>
       <c r="Q10" t="n">
-        <v>124982.21</v>
+        <v>169987.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9468055</v>
+        <v>9456627</v>
       </c>
       <c r="B11" t="n">
-        <v>1221</v>
+        <v>1511</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>364747.57</v>
+        <v>376381.87</v>
       </c>
       <c r="E11" t="n">
-        <v>304401.1</v>
+        <v>126290.67</v>
       </c>
       <c r="F11" t="n">
-        <v>257526.78</v>
-      </c>
-      <c r="G11" t="n">
-        <v>31325.06</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>9651.6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>9651.6</v>
-      </c>
+        <v>124982.21</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>355095.97</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>26472.9</v>
-      </c>
-      <c r="P11" t="n">
-        <v>26472.9</v>
-      </c>
+        <v>376381.87</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>283999.68</v>
+        <v>124982.21</v>
       </c>
     </row>
     <row r="12">
@@ -962,24 +944,24 @@
         <v>9468055</v>
       </c>
       <c r="B12" t="n">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>303520.57</v>
+        <v>364747.57</v>
       </c>
       <c r="E12" t="n">
-        <v>300305.3</v>
+        <v>304401.1</v>
       </c>
       <c r="F12" t="n">
-        <v>230397.28</v>
+        <v>257526.78</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>31325.06</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -988,28 +970,28 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>9651.6</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>9651.6</v>
       </c>
       <c r="M12" t="n">
-        <v>303520.57</v>
+        <v>355095.97</v>
       </c>
       <c r="N12" t="n">
-        <v>23722.79</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>26472.9</v>
       </c>
       <c r="P12" t="n">
-        <v>23722.79</v>
+        <v>26472.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>254120.07</v>
+        <v>283999.68</v>
       </c>
     </row>
     <row r="13">
@@ -1017,24 +999,24 @@
         <v>9468055</v>
       </c>
       <c r="B13" t="n">
-        <v>1481</v>
+        <v>1231</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>513818.81</v>
+        <v>336260.15</v>
       </c>
       <c r="E13" t="n">
-        <v>424704.55</v>
+        <v>300305.3</v>
       </c>
       <c r="F13" t="n">
-        <v>315943.56</v>
+        <v>230397.28</v>
       </c>
       <c r="G13" t="n">
-        <v>44810.88</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1052,19 +1034,19 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>513818.81</v>
+        <v>336260.15</v>
       </c>
       <c r="N13" t="n">
-        <v>1339.42</v>
+        <v>23722.79</v>
       </c>
       <c r="O13" t="n">
-        <v>37860.38</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>39199.8</v>
+        <v>23722.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>355143.36</v>
+        <v>254120.07</v>
       </c>
     </row>
     <row r="14">
@@ -1072,24 +1054,24 @@
         <v>9468055</v>
       </c>
       <c r="B14" t="n">
-        <v>1501</v>
+        <v>1481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4975358.49</v>
+        <v>513818.81</v>
       </c>
       <c r="E14" t="n">
-        <v>3652657.62</v>
+        <v>424862.65</v>
       </c>
       <c r="F14" t="n">
-        <v>3096359.39</v>
+        <v>359581.36</v>
       </c>
       <c r="G14" t="n">
-        <v>302674.08</v>
+        <v>44810.88</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1098,28 +1080,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>726037.97</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>726037.97</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4249320.52</v>
+        <v>513818.81</v>
       </c>
       <c r="N14" t="n">
-        <v>12856.3</v>
+        <v>1339.42</v>
       </c>
       <c r="O14" t="n">
-        <v>255763.76</v>
+        <v>37860.38</v>
       </c>
       <c r="P14" t="n">
-        <v>268620.06</v>
+        <v>39199.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3364979.45</v>
+        <v>398781.16</v>
       </c>
     </row>
     <row r="15">
@@ -1127,24 +1109,24 @@
         <v>9468055</v>
       </c>
       <c r="B15" t="n">
-        <v>4251</v>
+        <v>1501</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>524988.46</v>
+        <v>4975358.49</v>
       </c>
       <c r="E15" t="n">
-        <v>386219.63</v>
+        <v>3652657.62</v>
       </c>
       <c r="F15" t="n">
-        <v>325478.98</v>
+        <v>3093705.22</v>
       </c>
       <c r="G15" t="n">
-        <v>46987.59</v>
+        <v>302674.08</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1153,53 +1135,53 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>726037.97</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>726037.97</v>
       </c>
       <c r="M15" t="n">
-        <v>524988.46</v>
+        <v>4249320.52</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>12856.3</v>
       </c>
       <c r="O15" t="n">
-        <v>39709.36</v>
+        <v>255763.76</v>
       </c>
       <c r="P15" t="n">
-        <v>39709.36</v>
+        <v>268620.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>365188.34</v>
+        <v>3362325.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9468057</v>
+        <v>9468055</v>
       </c>
       <c r="B16" t="n">
-        <v>1371</v>
+        <v>4251</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9593274.119999999</v>
+        <v>524988.46</v>
       </c>
       <c r="E16" t="n">
-        <v>9027832.08</v>
+        <v>441205.77</v>
       </c>
       <c r="F16" t="n">
-        <v>7624144.79</v>
+        <v>372023.36</v>
       </c>
       <c r="G16" t="n">
-        <v>565340.29</v>
+        <v>46987.59</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1217,44 +1199,44 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>9593274.119999999</v>
+        <v>524988.46</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>476940.26</v>
+        <v>39709.36</v>
       </c>
       <c r="P16" t="n">
-        <v>476940.26</v>
+        <v>39709.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>8101085.05</v>
+        <v>411732.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>9470658</v>
+        <v>9468057</v>
       </c>
       <c r="B17" t="n">
-        <v>1231</v>
+        <v>1371</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2592199.31</v>
+        <v>10849751.62</v>
       </c>
       <c r="E17" t="n">
-        <v>296909.12</v>
+        <v>10284309.58</v>
       </c>
       <c r="F17" t="n">
-        <v>296909.12</v>
+        <v>7624144.79</v>
       </c>
       <c r="G17" t="n">
-        <v>911541.98</v>
+        <v>565340.29</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1263,53 +1245,53 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1383748.21</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1383748.21</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1208451.1</v>
+        <v>10849751.62</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>878501.92</v>
+        <v>476940.26</v>
       </c>
       <c r="P17" t="n">
-        <v>878501.92</v>
+        <v>476940.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1175411.04</v>
+        <v>8101085.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9473170</v>
+        <v>9470658</v>
       </c>
       <c r="B18" t="n">
-        <v>2301</v>
+        <v>1231</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>736365.61</v>
+        <v>2592199.31</v>
       </c>
       <c r="E18" t="n">
-        <v>350401.39</v>
+        <v>296909.12</v>
       </c>
       <c r="F18" t="n">
-        <v>350401.39</v>
+        <v>296909.12</v>
       </c>
       <c r="G18" t="n">
-        <v>188341.65</v>
+        <v>911541.98</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1318,53 +1300,53 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>197622.57</v>
+        <v>1383748.21</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>197622.57</v>
+        <v>1383748.21</v>
       </c>
       <c r="M18" t="n">
-        <v>538743.04</v>
+        <v>1208451.1</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>188341.65</v>
+        <v>878501.92</v>
       </c>
       <c r="P18" t="n">
-        <v>188341.65</v>
+        <v>878501.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>538743.04</v>
+        <v>1175411.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9473171</v>
+        <v>9473170</v>
       </c>
       <c r="B19" t="n">
-        <v>1221</v>
+        <v>2301</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14921954.12</v>
+        <v>736365.61</v>
       </c>
       <c r="E19" t="n">
-        <v>4183033.98</v>
+        <v>350401.39</v>
       </c>
       <c r="F19" t="n">
-        <v>3790571.98</v>
+        <v>350401.39</v>
       </c>
       <c r="G19" t="n">
-        <v>2567037.2</v>
+        <v>188341.65</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1373,53 +1355,53 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>197622.57</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>197622.57</v>
       </c>
       <c r="M19" t="n">
-        <v>14921954.12</v>
+        <v>538743.04</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2491527.64</v>
+        <v>188341.65</v>
       </c>
       <c r="P19" t="n">
-        <v>2491527.64</v>
+        <v>188341.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>6282099.62</v>
+        <v>538743.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9474703</v>
+        <v>9473171</v>
       </c>
       <c r="B20" t="n">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79058892.34999999</v>
+        <v>14921954.12</v>
       </c>
       <c r="E20" t="n">
-        <v>78541892.26000001</v>
+        <v>4185468.88</v>
       </c>
       <c r="F20" t="n">
-        <v>77547634.67</v>
+        <v>4177602.88</v>
       </c>
       <c r="G20" t="n">
-        <v>517000</v>
+        <v>3019937.2</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1428,87 +1410,105 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>79058892.26000001</v>
+        <v>14921954.12</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>509950</v>
+        <v>2903278.44</v>
       </c>
       <c r="P20" t="n">
-        <v>509950</v>
+        <v>2903278.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>78057584.67</v>
+        <v>7080881.32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9480259</v>
+        <v>9474703</v>
       </c>
       <c r="B21" t="n">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8657552.060000001</v>
+        <v>79058892.34999999</v>
       </c>
       <c r="E21" t="n">
-        <v>8529258.880000001</v>
+        <v>78541892.26000001</v>
       </c>
       <c r="F21" t="n">
-        <v>8529620.880000001</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+        <v>77547634.67</v>
+      </c>
+      <c r="G21" t="n">
+        <v>517000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.09</v>
+      </c>
       <c r="M21" t="n">
-        <v>8657552.060000001</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+        <v>79058892.26000001</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>509950</v>
+      </c>
+      <c r="P21" t="n">
+        <v>509950</v>
+      </c>
       <c r="Q21" t="n">
-        <v>8529620.880000001</v>
+        <v>78057584.67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>9480440</v>
+        <v>9480259</v>
       </c>
       <c r="B22" t="n">
-        <v>2241</v>
+        <v>1221</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8635921.619999999</v>
+        <v>8657552.060000001</v>
       </c>
       <c r="E22" t="n">
-        <v>8635921.619999999</v>
+        <v>8539867.949999999</v>
       </c>
       <c r="F22" t="n">
-        <v>8635921.619999999</v>
+        <v>8540229.949999999</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -1517,35 +1517,35 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>8635921.619999999</v>
+        <v>8657552.060000001</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
-        <v>8635921.619999999</v>
+        <v>8540229.949999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>9493230</v>
+        <v>9480440</v>
       </c>
       <c r="B23" t="n">
-        <v>1071</v>
+        <v>2241</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3500000</v>
+        <v>8635921.619999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>8635921.619999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>8635921.619999999</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1554,18 +1554,18 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>3500000</v>
+        <v>8635921.619999999</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>8635921.619999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>9493391</v>
+        <v>9493230</v>
       </c>
       <c r="B24" t="n">
         <v>1071</v>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11399338.2</v>
+        <v>3500000</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1591,7 +1591,7 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>11399338.2</v>
+        <v>3500000</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1602,24 +1602,24 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>9501912</v>
+        <v>9493391</v>
       </c>
       <c r="B25" t="n">
-        <v>1301</v>
+        <v>1071</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18665002.7</v>
+        <v>11399338.2</v>
       </c>
       <c r="E25" t="n">
-        <v>18665002.7</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>4477456.36</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1628,35 +1628,35 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>18665002.7</v>
+        <v>11399338.2</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
-        <v>4477456.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>9501917</v>
+        <v>9494511</v>
       </c>
       <c r="B26" t="n">
-        <v>1491</v>
+        <v>1511</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7500000</v>
+        <v>3930785.97</v>
       </c>
       <c r="E26" t="n">
-        <v>7500000</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>3750000</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1665,12 +1665,86 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>7500000</v>
+        <v>3930785.97</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9501912</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1301</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>18665002.7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>18665002.7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5599500.81</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>18665002.7</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>5599500.81</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9501917</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1491</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="n">
         <v>3750000</v>
       </c>
     </row>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -665,13 +665,13 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>377200278.81</v>
+        <v>392200278.81</v>
       </c>
       <c r="E7">
         <v>191344942.33</v>
       </c>
       <c r="F7">
-        <v>176169986.22</v>
+        <v>184414441.97</v>
       </c>
       <c r="G7">
         <v>19134958.28</v>
@@ -692,7 +692,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M7">
-        <v>366574561.2</v>
+        <v>381574561.2</v>
       </c>
       <c r="N7">
         <v>5029440.01</v>
@@ -704,7 +704,7 @@
         <v>23960764.92</v>
       </c>
       <c r="Q7">
-        <v>200130751.14</v>
+        <v>208375206.89</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1061,13 +1061,13 @@
         <v>18</v>
       </c>
       <c r="D16">
-        <v>524988.46</v>
+        <v>525179.9300000001</v>
       </c>
       <c r="E16">
-        <v>441205.77</v>
+        <v>441397.24</v>
       </c>
       <c r="F16">
-        <v>372023.36</v>
+        <v>372214.83</v>
       </c>
       <c r="G16">
         <v>46987.59</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>524988.46</v>
+        <v>525179.9300000001</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -1100,7 +1100,7 @@
         <v>39709.36</v>
       </c>
       <c r="Q16">
-        <v>411732.72</v>
+        <v>411924.19</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1120,7 +1120,7 @@
         <v>10284309.58</v>
       </c>
       <c r="F17">
-        <v>7624144.79</v>
+        <v>8685565.02</v>
       </c>
       <c r="G17">
         <v>565340.29</v>
@@ -1153,7 +1153,7 @@
         <v>476940.26</v>
       </c>
       <c r="Q17">
-        <v>8101085.05</v>
+        <v>9162505.279999999</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1282,7 +1282,7 @@
         <v>4177602.88</v>
       </c>
       <c r="G20">
-        <v>3446180.8</v>
+        <v>3487588.8</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="O20">
-        <v>3291632.17</v>
+        <v>3328982.19</v>
       </c>
       <c r="P20">
-        <v>3291632.17</v>
+        <v>3328982.19</v>
       </c>
       <c r="Q20">
-        <v>7469235.05</v>
+        <v>7506585.07</v>
       </c>
     </row>
     <row r="21" spans="1:17">

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -560,7 +560,7 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>6030471.4</v>
+        <v>6039081.21</v>
       </c>
       <c r="E4">
         <v>6028400.95</v>
@@ -569,7 +569,7 @@
         <v>5528400.95</v>
       </c>
       <c r="M4">
-        <v>6030471.4</v>
+        <v>6039081.21</v>
       </c>
       <c r="Q4">
         <v>5528400.95</v>
@@ -665,13 +665,13 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>392200278.81</v>
+        <v>396112653.73</v>
       </c>
       <c r="E7">
-        <v>191344942.33</v>
+        <v>204385725.92</v>
       </c>
       <c r="F7">
-        <v>184414441.97</v>
+        <v>196737272.3</v>
       </c>
       <c r="G7">
         <v>19134958.28</v>
@@ -692,7 +692,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M7">
-        <v>381574561.2</v>
+        <v>385486936.12</v>
       </c>
       <c r="N7">
         <v>5029440.01</v>
@@ -704,7 +704,7 @@
         <v>23960764.92</v>
       </c>
       <c r="Q7">
-        <v>208375206.89</v>
+        <v>220698037.22</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -718,7 +718,7 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>63156.57</v>
+        <v>68156.57000000001</v>
       </c>
       <c r="E8">
         <v>63156.57</v>
@@ -727,7 +727,7 @@
         <v>52124.13</v>
       </c>
       <c r="M8">
-        <v>63156.57</v>
+        <v>68156.57000000001</v>
       </c>
       <c r="Q8">
         <v>52124.13</v>
@@ -823,7 +823,7 @@
         <v>24</v>
       </c>
       <c r="D11">
-        <v>376381.87</v>
+        <v>394234.45</v>
       </c>
       <c r="E11">
         <v>132788.89</v>
@@ -832,7 +832,7 @@
         <v>131463.65</v>
       </c>
       <c r="M11">
-        <v>376381.87</v>
+        <v>394234.45</v>
       </c>
       <c r="Q11">
         <v>131463.65</v>
@@ -905,10 +905,10 @@
         <v>336260.15</v>
       </c>
       <c r="E13">
-        <v>300305.3</v>
+        <v>334453.39</v>
       </c>
       <c r="F13">
-        <v>230397.28</v>
+        <v>259314</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>23722.79</v>
       </c>
       <c r="Q13">
-        <v>254120.07</v>
+        <v>283036.79</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -955,7 +955,7 @@
         <v>26</v>
       </c>
       <c r="D14">
-        <v>513818.81</v>
+        <v>548795.22</v>
       </c>
       <c r="E14">
         <v>424862.65</v>
@@ -982,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>513818.81</v>
+        <v>548795.22</v>
       </c>
       <c r="N14">
         <v>1339.42</v>
@@ -1008,10 +1008,10 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>4975389.77</v>
+        <v>4975195.27</v>
       </c>
       <c r="E15">
-        <v>3652688.9</v>
+        <v>3652494.4</v>
       </c>
       <c r="F15">
         <v>3093736.5</v>
@@ -1026,16 +1026,16 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>726037.97</v>
+        <v>752609.76</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>726037.97</v>
+        <v>752609.76</v>
       </c>
       <c r="M15">
-        <v>4249351.8</v>
+        <v>4222585.51</v>
       </c>
       <c r="N15">
         <v>12856.3</v>
@@ -1061,7 +1061,7 @@
         <v>18</v>
       </c>
       <c r="D16">
-        <v>525179.9300000001</v>
+        <v>576526.13</v>
       </c>
       <c r="E16">
         <v>441397.24</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>525179.9300000001</v>
+        <v>576526.13</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>25</v>
       </c>
       <c r="D20">
-        <v>14921954.12</v>
+        <v>14999634.32</v>
       </c>
       <c r="E20">
         <v>4185468.88</v>
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>14921954.12</v>
+        <v>14999634.32</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -1379,7 +1379,7 @@
         <v>25</v>
       </c>
       <c r="D22">
-        <v>8657552.060000001</v>
+        <v>8687330.92</v>
       </c>
       <c r="E22">
         <v>8541476.75</v>
@@ -1388,7 +1388,7 @@
         <v>8541838.75</v>
       </c>
       <c r="M22">
-        <v>8657552.060000001</v>
+        <v>8687330.92</v>
       </c>
       <c r="Q22">
         <v>8541838.75</v>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -534,7 +534,7 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>353586.41</v>
+        <v>435092.93</v>
       </c>
       <c r="E3">
         <v>345872.73</v>
@@ -543,7 +543,7 @@
         <v>345872.73</v>
       </c>
       <c r="M3">
-        <v>353586.41</v>
+        <v>435092.93</v>
       </c>
       <c r="Q3">
         <v>345872.73</v>
@@ -560,7 +560,7 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>6039081.21</v>
+        <v>6067365.65</v>
       </c>
       <c r="E4">
         <v>6028400.95</v>
@@ -569,7 +569,7 @@
         <v>5528400.95</v>
       </c>
       <c r="M4">
-        <v>6039081.21</v>
+        <v>6067365.65</v>
       </c>
       <c r="Q4">
         <v>5528400.95</v>
@@ -665,10 +665,10 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>396112653.73</v>
+        <v>392384605.59</v>
       </c>
       <c r="E7">
-        <v>204385725.92</v>
+        <v>208264264.15</v>
       </c>
       <c r="F7">
         <v>196737272.3</v>
@@ -692,7 +692,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M7">
-        <v>385486936.12</v>
+        <v>381758887.98</v>
       </c>
       <c r="N7">
         <v>5029440.01</v>
@@ -718,7 +718,7 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>68156.57000000001</v>
+        <v>80880.28</v>
       </c>
       <c r="E8">
         <v>63156.57</v>
@@ -727,7 +727,7 @@
         <v>52124.13</v>
       </c>
       <c r="M8">
-        <v>68156.57000000001</v>
+        <v>80880.28</v>
       </c>
       <c r="Q8">
         <v>52124.13</v>
@@ -852,10 +852,10 @@
         <v>398978.37</v>
       </c>
       <c r="E12">
-        <v>304401.1</v>
+        <v>338631.9</v>
       </c>
       <c r="F12">
-        <v>257526.78</v>
+        <v>286513.15</v>
       </c>
       <c r="G12">
         <v>31325.06</v>
@@ -888,7 +888,7 @@
         <v>26472.9</v>
       </c>
       <c r="Q12">
-        <v>283999.68</v>
+        <v>312986.05</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -902,7 +902,7 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>336260.15</v>
+        <v>340018.05</v>
       </c>
       <c r="E13">
         <v>334453.39</v>
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>336260.15</v>
+        <v>340018.05</v>
       </c>
       <c r="N13">
         <v>23722.79</v>
@@ -1008,13 +1008,13 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>4975195.27</v>
+        <v>4976702.57</v>
       </c>
       <c r="E15">
-        <v>3652494.4</v>
+        <v>3657932.55</v>
       </c>
       <c r="F15">
-        <v>3093736.5</v>
+        <v>3097296.27</v>
       </c>
       <c r="G15">
         <v>302674.08</v>
@@ -1035,7 +1035,7 @@
         <v>752609.76</v>
       </c>
       <c r="M15">
-        <v>4222585.51</v>
+        <v>4224092.81</v>
       </c>
       <c r="N15">
         <v>12856.3</v>
@@ -1047,7 +1047,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q15">
-        <v>3362356.56</v>
+        <v>3365916.33</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1276,13 +1276,13 @@
         <v>14999634.32</v>
       </c>
       <c r="E20">
-        <v>4185468.88</v>
+        <v>4265583.98</v>
       </c>
       <c r="F20">
-        <v>4177602.88</v>
+        <v>4255758.52</v>
       </c>
       <c r="G20">
-        <v>3487588.8</v>
+        <v>3642868.8</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="O20">
-        <v>3328982.19</v>
+        <v>3469044.75</v>
       </c>
       <c r="P20">
-        <v>3328982.19</v>
+        <v>3469044.75</v>
       </c>
       <c r="Q20">
-        <v>7506585.07</v>
+        <v>7724803.27</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1382,16 +1382,16 @@
         <v>8687330.92</v>
       </c>
       <c r="E22">
-        <v>8541476.75</v>
+        <v>8571255.609999999</v>
       </c>
       <c r="F22">
-        <v>8541838.75</v>
+        <v>8571617.609999999</v>
       </c>
       <c r="M22">
         <v>8687330.92</v>
       </c>
       <c r="Q22">
-        <v>8541838.75</v>
+        <v>8571617.609999999</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1457,16 +1457,16 @@
         <v>30</v>
       </c>
       <c r="D25">
-        <v>11399338.2</v>
+        <v>11407168.95</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>7830.75</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>11399338.2</v>
+        <v>11407168.95</v>
       </c>
       <c r="Q25">
         <v>0</v>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>392384605.59</v>
+        <v>384553096.83</v>
       </c>
       <c r="E7" t="n">
-        <v>209420836.4</v>
+        <v>213607749.28</v>
       </c>
       <c r="F7" t="n">
-        <v>201142918.74</v>
+        <v>202296715.24</v>
       </c>
       <c r="G7" t="n">
         <v>19134958.28</v>
@@ -758,7 +758,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M7" t="n">
-        <v>381758887.98</v>
+        <v>373927379.22</v>
       </c>
       <c r="N7" t="n">
         <v>5029440.01</v>
@@ -770,7 +770,7 @@
         <v>23960764.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>225103683.66</v>
+        <v>226257480.16</v>
       </c>
     </row>
     <row r="8">
@@ -918,7 +918,7 @@
         <v>586046.0699999999</v>
       </c>
       <c r="E11" t="n">
-        <v>132788.89</v>
+        <v>156213.57</v>
       </c>
       <c r="F11" t="n">
         <v>131463.65</v>
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>550595.9</v>
+        <v>668015.75</v>
       </c>
       <c r="E14" t="n">
-        <v>461720.76</v>
+        <v>477035.48</v>
       </c>
       <c r="F14" t="n">
-        <v>389263.75</v>
+        <v>403756.93</v>
       </c>
       <c r="G14" t="n">
         <v>44810.88</v>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>550595.9</v>
+        <v>668015.75</v>
       </c>
       <c r="N14" t="n">
         <v>1339.42</v>
@@ -1101,7 +1101,7 @@
         <v>39199.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>428463.55</v>
+        <v>442956.73</v>
       </c>
     </row>
     <row r="15">
@@ -1120,10 +1120,10 @@
         <v>5949390.46</v>
       </c>
       <c r="E15" t="n">
-        <v>4177895.33</v>
+        <v>4180635.08</v>
       </c>
       <c r="F15" t="n">
-        <v>3543094.94</v>
+        <v>3545834.69</v>
       </c>
       <c r="G15" t="n">
         <v>302674.08</v>
@@ -1156,7 +1156,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>3811715</v>
+        <v>3814454.75</v>
       </c>
     </row>
     <row r="16">
@@ -1178,7 +1178,7 @@
         <v>499787.01</v>
       </c>
       <c r="F16" t="n">
-        <v>372214.83</v>
+        <v>421625.07</v>
       </c>
       <c r="G16" t="n">
         <v>46987.59</v>
@@ -1211,7 +1211,7 @@
         <v>39709.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>411924.19</v>
+        <v>461334.43</v>
       </c>
     </row>
     <row r="17">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10849751.62</v>
+        <v>11144098.09</v>
       </c>
       <c r="E17" t="n">
         <v>10284309.58</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>10849751.62</v>
+        <v>11144098.09</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1401,7 +1401,7 @@
         <v>4531758.52</v>
       </c>
       <c r="G20" t="n">
-        <v>3642868.8</v>
+        <v>3720508.8</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3469044.75</v>
+        <v>3539076.03</v>
       </c>
       <c r="P20" t="n">
-        <v>3469044.75</v>
+        <v>3539076.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>8000803.27</v>
+        <v>8070834.55</v>
       </c>
     </row>
     <row r="21">
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8687330.92</v>
+        <v>8838530.92</v>
       </c>
       <c r="E22" t="n">
         <v>8579660.08</v>
@@ -1517,7 +1517,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>8687330.92</v>
+        <v>8838530.92</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
